--- a/Compititor's_Price/Celotex_Prices/Celotex_Prices_04-03-2026.xlsx
+++ b/Compititor's_Price/Celotex_Prices/Celotex_Prices_04-03-2026.xlsx
@@ -2438,7 +2438,7 @@
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>£42.15</t>
+          <t>Price Not Found</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
